--- a/Company_Placement_Dataset.xlsx
+++ b/Company_Placement_Dataset.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Student_ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -469,7 +469,7 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Placement_Status</t>
+          <t>Placement</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
@@ -481,26 +481,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sneha_1</t>
+          <t>STU001</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.61</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="C2" t="n">
+        <v>41</v>
+      </c>
+      <c r="D2" t="n">
+        <v>87</v>
+      </c>
+      <c r="E2" t="n">
         <v>57</v>
       </c>
-      <c r="D2" t="n">
-        <v>55</v>
-      </c>
-      <c r="E2" t="n">
-        <v>59</v>
-      </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="J2" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -525,23 +525,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Priya_2</t>
+          <t>STU002</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.63</v>
+        <v>8.83</v>
       </c>
       <c r="C3" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="D3" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E3" t="n">
         <v>77</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -552,10 +552,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="J3" t="n">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -569,26 +569,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Harsha_3</t>
+          <t>STU003</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.35</v>
+        <v>6.55</v>
       </c>
       <c r="C4" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D4" t="n">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="E4" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -596,10 +596,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="J4" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -613,81 +613,81 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Rohit_4</t>
+          <t>STU004</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.45</v>
+        <v>8.15</v>
       </c>
       <c r="C5" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D5" t="n">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="E5" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>81</v>
       </c>
       <c r="J5" t="n">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Meena_5</t>
+          <t>STU005</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.16</v>
+        <v>9.81</v>
       </c>
       <c r="C6" t="n">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="D6" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E6" t="n">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="J6" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -701,37 +701,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arjun_6</t>
+          <t>STU006</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.93</v>
+        <v>6.69</v>
       </c>
       <c r="C7" t="n">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="D7" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E7" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="J7" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -745,114 +745,114 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sai_7</t>
+          <t>STU007</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.9</v>
+        <v>6.82</v>
       </c>
       <c r="C8" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="D8" t="n">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J8" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meena_8</t>
+          <t>STU008</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.22</v>
+        <v>8.98</v>
       </c>
       <c r="C9" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="D9" t="n">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="J9" t="n">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>10.63</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sai_9</t>
+          <t>STU009</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.22</v>
+        <v>7.14</v>
       </c>
       <c r="C10" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D10" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E10" t="n">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -860,43 +860,43 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="J10" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Priya_10</t>
+          <t>STU010</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.51</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -904,40 +904,40 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="J11" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Neha_11</t>
+          <t>STU011</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9.359999999999999</v>
+        <v>5.75</v>
       </c>
       <c r="C12" t="n">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="E12" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
         <v>6</v>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="J12" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -965,26 +965,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Rohit_12</t>
+          <t>STU012</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6.59</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="E13" t="n">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -992,54 +992,54 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="J13" t="n">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>13.97</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rohit_13</t>
+          <t>STU013</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7.74</v>
+        <v>7.56</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="E14" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J14" t="n">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1053,23 +1053,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Divya_14</t>
+          <t>STU014</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.119999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E15" t="n">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
         <v>8</v>
@@ -1080,43 +1080,43 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="J15" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rahul_15</t>
+          <t>STU015</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8.49</v>
+        <v>5.99</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="D16" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="E16" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1124,87 +1124,87 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="J16" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Anjali_16</t>
+          <t>STU016</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7.5</v>
+        <v>7.61</v>
       </c>
       <c r="C17" t="n">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="E17" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="J17" t="n">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Placed</t>
+          <t>Not Placed</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pooja_17</t>
+          <t>STU017</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9.199999999999999</v>
+        <v>6.82</v>
       </c>
       <c r="C18" t="n">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E18" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1212,87 +1212,87 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="J18" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sandeep_18</t>
+          <t>STU018</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9.539999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="C19" t="n">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E19" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="J19" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pooja_19</t>
+          <t>STU019</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.55</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="D20" t="n">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="E20" t="n">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1300,131 +1300,131 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="J20" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>14.15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Harsha_20</t>
+          <t>STU020</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.869999999999999</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E21" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="J21" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Akash_21</t>
+          <t>STU021</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7.36</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="D22" t="n">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="E22" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="J22" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Meena_22</t>
+          <t>STU022</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7.43</v>
+        <v>6.69</v>
       </c>
       <c r="C23" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="D23" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="E23" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1432,98 +1432,98 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J23" t="n">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>14.94</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Neha_23</t>
+          <t>STU023</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7.94</v>
+        <v>8.42</v>
       </c>
       <c r="C24" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D24" t="n">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="E24" t="n">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="F24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" t="n">
         <v>1</v>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J24" t="n">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Priya_24</t>
+          <t>STU024</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9.279999999999999</v>
+        <v>8.15</v>
       </c>
       <c r="C25" t="n">
+        <v>54</v>
+      </c>
+      <c r="D25" t="n">
+        <v>77</v>
+      </c>
+      <c r="E25" t="n">
+        <v>54</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>74</v>
+      </c>
+      <c r="J25" t="n">
         <v>44</v>
-      </c>
-      <c r="D25" t="n">
-        <v>72</v>
-      </c>
-      <c r="E25" t="n">
-        <v>60</v>
-      </c>
-      <c r="F25" t="n">
-        <v>3</v>
-      </c>
-      <c r="G25" t="n">
-        <v>7</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>87</v>
-      </c>
-      <c r="J25" t="n">
-        <v>48</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1537,20 +1537,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Neha_25</t>
+          <t>STU025</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>8.039999999999999</v>
+        <v>9.57</v>
       </c>
       <c r="C26" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="D26" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="E26" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
@@ -1560,102 +1560,102 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="J26" t="n">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>9.470000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Divya_26</t>
+          <t>STU026</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.06</v>
+        <v>8.76</v>
       </c>
       <c r="C27" t="n">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E27" t="n">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="F27" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="J27" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Vikram_27</t>
+          <t>STU027</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9.02</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="C28" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="D28" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E28" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="J28" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1669,26 +1669,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Anjali_28</t>
+          <t>STU028</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6.73</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="D29" t="n">
         <v>95</v>
       </c>
       <c r="E29" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1696,219 +1696,219 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="J29" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Harsha_29</t>
+          <t>STU029</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>9.18</v>
+        <v>6.33</v>
       </c>
       <c r="C30" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="D30" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="E30" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="J30" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kiran_30</t>
+          <t>STU030</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>9.300000000000001</v>
+        <v>9.26</v>
       </c>
       <c r="C31" t="n">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="D31" t="n">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="E31" t="n">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J31" t="n">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Varun_31</t>
+          <t>STU031</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>6.76</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="C32" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D32" t="n">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="E32" t="n">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I32" t="n">
         <v>76</v>
       </c>
       <c r="J32" t="n">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>12.41</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kiran_32</t>
+          <t>STU032</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>9.76</v>
+        <v>7.55</v>
       </c>
       <c r="C33" t="n">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D33" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E33" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J33" t="n">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Keerthi_33</t>
+          <t>STU033</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7.71</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="D34" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E34" t="n">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1916,37 +1916,37 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="J34" t="n">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>8.720000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Arjun_34</t>
+          <t>STU034</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>8.119999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D35" t="n">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="E35" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="F35" t="n">
         <v>4</v>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="J35" t="n">
         <v>78</v>
@@ -1977,37 +1977,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Priya_35</t>
+          <t>STU035</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>8.23</v>
+        <v>5.81</v>
       </c>
       <c r="C36" t="n">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="D36" t="n">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="E36" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="F36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I36" t="n">
         <v>99</v>
       </c>
       <c r="J36" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2021,111 +2021,111 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kiran_36</t>
+          <t>STU036</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>8.449999999999999</v>
+        <v>7.39</v>
       </c>
       <c r="C37" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="D37" t="n">
+        <v>76</v>
+      </c>
+      <c r="E37" t="n">
+        <v>73</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>4</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>80</v>
+      </c>
+      <c r="J37" t="n">
         <v>55</v>
       </c>
-      <c r="E37" t="n">
-        <v>61</v>
-      </c>
-      <c r="F37" t="n">
-        <v>4</v>
-      </c>
-      <c r="G37" t="n">
-        <v>2</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>84</v>
-      </c>
-      <c r="J37" t="n">
-        <v>60</v>
-      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Arjun_37</t>
+          <t>STU037</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5.54</v>
+        <v>6.09</v>
       </c>
       <c r="C38" t="n">
+        <v>81</v>
+      </c>
+      <c r="D38" t="n">
+        <v>59</v>
+      </c>
+      <c r="E38" t="n">
+        <v>69</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>89</v>
+      </c>
+      <c r="J38" t="n">
         <v>79</v>
       </c>
-      <c r="D38" t="n">
-        <v>76</v>
-      </c>
-      <c r="E38" t="n">
-        <v>51</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" t="n">
-        <v>8</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>86</v>
-      </c>
-      <c r="J38" t="n">
-        <v>56</v>
-      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>14.98</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Rohit_38</t>
+          <t>STU038</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>9.609999999999999</v>
+        <v>9.98</v>
       </c>
       <c r="C39" t="n">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="D39" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E39" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G39" t="n">
         <v>4</v>
@@ -2136,43 +2136,43 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J39" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Harsha_39</t>
+          <t>STU039</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="C40" t="n">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="D40" t="n">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="E40" t="n">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="F40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>99</v>
       </c>
       <c r="J40" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2191,43 +2191,43 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>5.18</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Rohit_40</t>
+          <t>STU040</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>6.66</v>
+        <v>5.54</v>
       </c>
       <c r="C41" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D41" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="E41" t="n">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="F41" t="n">
         <v>5</v>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J41" t="n">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2241,152 +2241,152 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Kiran_41</t>
+          <t>STU041</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>8.66</v>
+        <v>9.5</v>
       </c>
       <c r="C42" t="n">
+        <v>87</v>
+      </c>
+      <c r="D42" t="n">
+        <v>75</v>
+      </c>
+      <c r="E42" t="n">
+        <v>49</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" t="n">
+        <v>4</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>81</v>
+      </c>
+      <c r="J42" t="n">
         <v>53</v>
       </c>
-      <c r="D42" t="n">
-        <v>83</v>
-      </c>
-      <c r="E42" t="n">
-        <v>85</v>
-      </c>
-      <c r="F42" t="n">
-        <v>3</v>
-      </c>
-      <c r="G42" t="n">
-        <v>8</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>78</v>
-      </c>
-      <c r="J42" t="n">
-        <v>97</v>
-      </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Priya_42</t>
+          <t>STU042</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5.91</v>
+        <v>9.34</v>
       </c>
       <c r="C43" t="n">
+        <v>72</v>
+      </c>
+      <c r="D43" t="n">
+        <v>71</v>
+      </c>
+      <c r="E43" t="n">
+        <v>56</v>
+      </c>
+      <c r="F43" t="n">
+        <v>6</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>100</v>
+      </c>
+      <c r="J43" t="n">
         <v>67</v>
       </c>
-      <c r="D43" t="n">
-        <v>93</v>
-      </c>
-      <c r="E43" t="n">
-        <v>62</v>
-      </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
-        <v>94</v>
-      </c>
-      <c r="J43" t="n">
-        <v>48</v>
-      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>12.95</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Nikhil_43</t>
+          <t>STU043</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>6.21</v>
+        <v>5.7</v>
       </c>
       <c r="C44" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D44" t="n">
+        <v>89</v>
+      </c>
+      <c r="E44" t="n">
+        <v>48</v>
+      </c>
+      <c r="F44" t="n">
+        <v>5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>4</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>88</v>
+      </c>
+      <c r="J44" t="n">
         <v>75</v>
       </c>
-      <c r="E44" t="n">
-        <v>90</v>
-      </c>
-      <c r="F44" t="n">
-        <v>4</v>
-      </c>
-      <c r="G44" t="n">
-        <v>8</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>73</v>
-      </c>
-      <c r="J44" t="n">
-        <v>44</v>
-      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>11.47</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Rohit_44</t>
+          <t>STU044</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>7.9</v>
+        <v>8.02</v>
       </c>
       <c r="C45" t="n">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="D45" t="n">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="E45" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="F45" t="n">
         <v>5</v>
@@ -2396,190 +2396,190 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="J45" t="n">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>9.630000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Pooja_45</t>
+          <t>STU045</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>7.1</v>
+        <v>7.43</v>
       </c>
       <c r="C46" t="n">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="D46" t="n">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="E46" t="n">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="J46" t="n">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Placed</t>
+          <t>Not Placed</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>9.220000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Meena_46</t>
+          <t>STU046</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>8.93</v>
+        <v>6.62</v>
       </c>
       <c r="C47" t="n">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="D47" t="n">
+        <v>62</v>
+      </c>
+      <c r="E47" t="n">
+        <v>89</v>
+      </c>
+      <c r="F47" t="n">
+        <v>4</v>
+      </c>
+      <c r="G47" t="n">
+        <v>6</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>75</v>
+      </c>
+      <c r="J47" t="n">
         <v>95</v>
       </c>
-      <c r="E47" t="n">
-        <v>71</v>
-      </c>
-      <c r="F47" t="n">
-        <v>5</v>
-      </c>
-      <c r="G47" t="n">
-        <v>2</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>97</v>
-      </c>
-      <c r="J47" t="n">
-        <v>50</v>
-      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>Placed</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>12.76</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Anjali_47</t>
+          <t>STU047</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>9.380000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="C48" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D48" t="n">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="E48" t="n">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J48" t="n">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>11.04</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sneha_48</t>
+          <t>STU048</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7.18</v>
+        <v>8.81</v>
       </c>
       <c r="C49" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D49" t="n">
+        <v>57</v>
+      </c>
+      <c r="E49" t="n">
+        <v>50</v>
+      </c>
+      <c r="F49" t="n">
+        <v>6</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>62</v>
+      </c>
+      <c r="J49" t="n">
         <v>94</v>
-      </c>
-      <c r="E49" t="n">
-        <v>75</v>
-      </c>
-      <c r="F49" t="n">
-        <v>2</v>
-      </c>
-      <c r="G49" t="n">
-        <v>3</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>81</v>
-      </c>
-      <c r="J49" t="n">
-        <v>59</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2593,81 +2593,81 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sai_49</t>
+          <t>STU049</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>6.48</v>
+        <v>7.62</v>
       </c>
       <c r="C50" t="n">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="D50" t="n">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="E50" t="n">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="F50" t="n">
         <v>3</v>
       </c>
       <c r="G50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="J50" t="n">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Nikhil_50</t>
+          <t>STU050</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>7.05</v>
+        <v>6.37</v>
       </c>
       <c r="C51" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D51" t="n">
+        <v>57</v>
+      </c>
+      <c r="E51" t="n">
+        <v>95</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>4</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>92</v>
+      </c>
+      <c r="J51" t="n">
         <v>65</v>
-      </c>
-      <c r="E51" t="n">
-        <v>88</v>
-      </c>
-      <c r="F51" t="n">
-        <v>5</v>
-      </c>
-      <c r="G51" t="n">
-        <v>5</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>73</v>
-      </c>
-      <c r="J51" t="n">
-        <v>96</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -2681,26 +2681,26 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Nikhil_51</t>
+          <t>STU051</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>6.29</v>
+        <v>8.56</v>
       </c>
       <c r="C52" t="n">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D52" t="n">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="E52" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F52" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2708,131 +2708,131 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="J52" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>14.55</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Vikram_52</t>
+          <t>STU052</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7.42</v>
+        <v>6.69</v>
       </c>
       <c r="C53" t="n">
+        <v>46</v>
+      </c>
+      <c r="D53" t="n">
+        <v>78</v>
+      </c>
+      <c r="E53" t="n">
+        <v>67</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2</v>
+      </c>
+      <c r="G53" t="n">
+        <v>5</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>98</v>
+      </c>
+      <c r="J53" t="n">
         <v>72</v>
       </c>
-      <c r="D53" t="n">
-        <v>47</v>
-      </c>
-      <c r="E53" t="n">
-        <v>69</v>
-      </c>
-      <c r="F53" t="n">
-        <v>5</v>
-      </c>
-      <c r="G53" t="n">
-        <v>3</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>71</v>
-      </c>
-      <c r="J53" t="n">
-        <v>85</v>
-      </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Divya_53</t>
+          <t>STU053</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>5.51</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="C54" t="n">
+        <v>52</v>
+      </c>
+      <c r="D54" t="n">
+        <v>56</v>
+      </c>
+      <c r="E54" t="n">
+        <v>42</v>
+      </c>
+      <c r="F54" t="n">
+        <v>5</v>
+      </c>
+      <c r="G54" t="n">
+        <v>6</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>93</v>
+      </c>
+      <c r="J54" t="n">
         <v>99</v>
       </c>
-      <c r="D54" t="n">
-        <v>91</v>
-      </c>
-      <c r="E54" t="n">
-        <v>79</v>
-      </c>
-      <c r="F54" t="n">
-        <v>6</v>
-      </c>
-      <c r="G54" t="n">
-        <v>3</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>83</v>
-      </c>
-      <c r="J54" t="n">
-        <v>44</v>
-      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>12.68</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Vikram_54</t>
+          <t>STU054</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>8.24</v>
+        <v>8.59</v>
       </c>
       <c r="C55" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="D55" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E55" t="n">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="F55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2840,43 +2840,43 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="J55" t="n">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>14.39</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Vikram_55</t>
+          <t>STU055</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7.27</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="C56" t="n">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="D56" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="F56" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G56" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2884,43 +2884,43 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J56" t="n">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Anjali_56</t>
+          <t>STU056</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>8.210000000000001</v>
+        <v>6.97</v>
       </c>
       <c r="C57" t="n">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="D57" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E57" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2928,43 +2928,43 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="J57" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>11.98</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Neha_57</t>
+          <t>STU057</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>8.17</v>
+        <v>6.28</v>
       </c>
       <c r="C58" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="D58" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E58" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F58" t="n">
         <v>4</v>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="J58" t="n">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -2989,37 +2989,37 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Anjali_58</t>
+          <t>STU058</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>8.4</v>
+        <v>7.43</v>
       </c>
       <c r="C59" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="D59" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E59" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F59" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G59" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="J59" t="n">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -3027,32 +3027,32 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>10.58</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Pooja_59</t>
+          <t>STU059</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>6.49</v>
+        <v>7.63</v>
       </c>
       <c r="C60" t="n">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="D60" t="n">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="E60" t="n">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="F60" t="n">
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -3060,131 +3060,131 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J60" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Arjun_60</t>
+          <t>STU060</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>7.5</v>
+        <v>7.01</v>
       </c>
       <c r="C61" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D61" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E61" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="J61" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Rohit_61</t>
+          <t>STU061</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>8.390000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="C62" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D62" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="E62" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F62" t="n">
+        <v>6</v>
+      </c>
+      <c r="G62" t="n">
         <v>1</v>
       </c>
-      <c r="G62" t="n">
-        <v>6</v>
-      </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J62" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>10.56</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sandeep_62</t>
+          <t>STU062</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>7.54</v>
+        <v>6.37</v>
       </c>
       <c r="C63" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="D63" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="E63" t="n">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G63" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -3192,43 +3192,43 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="J63" t="n">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sandeep_63</t>
+          <t>STU063</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>9.85</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="C64" t="n">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="D64" t="n">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="E64" t="n">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="F64" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -3236,43 +3236,43 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="J64" t="n">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Placed</t>
+          <t>Not Placed</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>9.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Anjali_64</t>
+          <t>STU064</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>8.77</v>
+        <v>6.62</v>
       </c>
       <c r="C65" t="n">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D65" t="n">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="E65" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -3280,131 +3280,131 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J65" t="n">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>12.78</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Nikhil_65</t>
+          <t>STU065</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>7.44</v>
+        <v>9.51</v>
       </c>
       <c r="C66" t="n">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="D66" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="E66" t="n">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="J66" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Arjun_66</t>
+          <t>STU066</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>6.11</v>
+        <v>6.61</v>
       </c>
       <c r="C67" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="D67" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E67" t="n">
         <v>89</v>
       </c>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G67" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="J67" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Vikram_67</t>
+          <t>STU067</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>7.89</v>
+        <v>5.85</v>
       </c>
       <c r="C68" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D68" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E68" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G68" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="J68" t="n">
-        <v>96</v>
+        <v>49</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -3429,26 +3429,26 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Neha_68</t>
+          <t>STU068</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>7.17</v>
+        <v>6.54</v>
       </c>
       <c r="C69" t="n">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="D69" t="n">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="E69" t="n">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="F69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J69" t="n">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -3473,70 +3473,70 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Harsha_69</t>
+          <t>STU069</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>9.02</v>
+        <v>7.94</v>
       </c>
       <c r="C70" t="n">
+        <v>66</v>
+      </c>
+      <c r="D70" t="n">
+        <v>43</v>
+      </c>
+      <c r="E70" t="n">
+        <v>53</v>
+      </c>
+      <c r="F70" t="n">
+        <v>6</v>
+      </c>
+      <c r="G70" t="n">
+        <v>6</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
         <v>97</v>
       </c>
-      <c r="D70" t="n">
-        <v>54</v>
-      </c>
-      <c r="E70" t="n">
-        <v>76</v>
-      </c>
-      <c r="F70" t="n">
-        <v>2</v>
-      </c>
-      <c r="G70" t="n">
-        <v>4</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I70" t="n">
-        <v>85</v>
-      </c>
       <c r="J70" t="n">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ajay_70</t>
+          <t>STU070</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>6.98</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="C71" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D71" t="n">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="E71" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F71" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -3544,43 +3544,43 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="J71" t="n">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Akash_71</t>
+          <t>STU071</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>7.85</v>
+        <v>9.51</v>
       </c>
       <c r="C72" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D72" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E72" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F72" t="n">
         <v>5</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3588,43 +3588,43 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J72" t="n">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Rohit_72</t>
+          <t>STU072</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>9.31</v>
+        <v>7.69</v>
       </c>
       <c r="C73" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D73" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="E73" t="n">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="F73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3632,43 +3632,43 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="J73" t="n">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Vikram_73</t>
+          <t>STU073</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>8.85</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C74" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="D74" t="n">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="E74" t="n">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="F74" t="n">
         <v>4</v>
       </c>
       <c r="G74" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -3676,54 +3676,54 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J74" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Harsha_74</t>
+          <t>STU074</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>5.73</v>
+        <v>6.32</v>
       </c>
       <c r="C75" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="D75" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E75" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F75" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="J75" t="n">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -3737,26 +3737,26 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sai_75</t>
+          <t>STU075</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>6.38</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="C76" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="D76" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E76" t="n">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="F76" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G76" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -3764,54 +3764,54 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="J76" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Neha_76</t>
+          <t>STU076</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>9.67</v>
+        <v>7.93</v>
       </c>
       <c r="C77" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="D77" t="n">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="E77" t="n">
+        <v>54</v>
+      </c>
+      <c r="F77" t="n">
+        <v>5</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
         <v>61</v>
       </c>
-      <c r="F77" t="n">
-        <v>3</v>
-      </c>
-      <c r="G77" t="n">
-        <v>2</v>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I77" t="n">
-        <v>94</v>
-      </c>
       <c r="J77" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -3819,87 +3819,87 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>6.23</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Pooja_77</t>
+          <t>STU077</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>5.98</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="C78" t="n">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="D78" t="n">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="E78" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F78" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I78" t="n">
+        <v>96</v>
+      </c>
+      <c r="J78" t="n">
         <v>100</v>
       </c>
-      <c r="J78" t="n">
-        <v>85</v>
-      </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Kiran_78</t>
+          <t>STU078</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>5.83</v>
+        <v>8.65</v>
       </c>
       <c r="C79" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D79" t="n">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="E79" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G79" t="n">
         <v>1</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="J79" t="n">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -3913,26 +3913,26 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Akash_79</t>
+          <t>STU079</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>9.039999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="C80" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="D80" t="n">
+        <v>59</v>
+      </c>
+      <c r="E80" t="n">
         <v>76</v>
       </c>
-      <c r="E80" t="n">
-        <v>95</v>
-      </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3940,10 +3940,10 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="J80" t="n">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -3951,161 +3951,161 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>5.11</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Vikram_80</t>
+          <t>STU080</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>5.56</v>
+        <v>9.24</v>
       </c>
       <c r="C81" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="D81" t="n">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="E81" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G81" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I81" t="n">
+        <v>96</v>
+      </c>
+      <c r="J81" t="n">
         <v>90</v>
       </c>
-      <c r="J81" t="n">
-        <v>97</v>
-      </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Varun_81</t>
+          <t>STU081</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>8.609999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="C82" t="n">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D82" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="E82" t="n">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="F82" t="n">
+        <v>4</v>
+      </c>
+      <c r="G82" t="n">
         <v>5</v>
       </c>
-      <c r="G82" t="n">
-        <v>4</v>
-      </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J82" t="n">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Neha_82</t>
+          <t>STU082</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>6.68</v>
+        <v>7.45</v>
       </c>
       <c r="C83" t="n">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="D83" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="E83" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G83" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J83" t="n">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>11.81</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Varun_83</t>
+          <t>STU083</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>8.01</v>
+        <v>9.84</v>
       </c>
       <c r="C84" t="n">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="D84" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E84" t="n">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G84" t="n">
         <v>7</v>
@@ -4116,98 +4116,98 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="J84" t="n">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>11.77</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Kiran_84</t>
+          <t>STU084</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>7.06</v>
+        <v>6.71</v>
       </c>
       <c r="C85" t="n">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="D85" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E85" t="n">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="F85" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
         <v>4</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J85" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Kiran_85</t>
+          <t>STU085</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>5.88</v>
+        <v>8.25</v>
       </c>
       <c r="C86" t="n">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="D86" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E86" t="n">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="F86" t="n">
+        <v>3</v>
+      </c>
+      <c r="G86" t="n">
         <v>5</v>
       </c>
-      <c r="G86" t="n">
-        <v>3</v>
-      </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J86" t="n">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -4221,26 +4221,26 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Keerthi_86</t>
+          <t>STU086</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>7.47</v>
+        <v>7.1</v>
       </c>
       <c r="C87" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D87" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="E87" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F87" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G87" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -4248,43 +4248,43 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="J87" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Neha_87</t>
+          <t>STU087</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>7.12</v>
+        <v>6.59</v>
       </c>
       <c r="C88" t="n">
+        <v>66</v>
+      </c>
+      <c r="D88" t="n">
+        <v>71</v>
+      </c>
+      <c r="E88" t="n">
         <v>75</v>
       </c>
-      <c r="D88" t="n">
-        <v>73</v>
-      </c>
-      <c r="E88" t="n">
-        <v>67</v>
-      </c>
       <c r="F88" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G88" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -4292,43 +4292,43 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J88" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Varun_88</t>
+          <t>STU088</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>6.69</v>
+        <v>5.92</v>
       </c>
       <c r="C89" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D89" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="E89" t="n">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="F89" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -4336,10 +4336,10 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="J89" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -4353,26 +4353,26 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Harsha_89</t>
+          <t>STU089</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>9.68</v>
+        <v>7.89</v>
       </c>
       <c r="C90" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="D90" t="n">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="E90" t="n">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F90" t="n">
         <v>2</v>
       </c>
       <c r="G90" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -4380,54 +4380,54 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="J90" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sandeep_90</t>
+          <t>STU090</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>8.130000000000001</v>
+        <v>6.04</v>
       </c>
       <c r="C91" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D91" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="E91" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F91" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G91" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J91" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -4441,23 +4441,23 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Rahul_91</t>
+          <t>STU091</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>8.619999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="C92" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D92" t="n">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="E92" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G92" t="n">
         <v>8</v>
@@ -4468,54 +4468,54 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="J92" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Rohit_92</t>
+          <t>STU092</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>8.31</v>
+        <v>6.52</v>
       </c>
       <c r="C93" t="n">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="D93" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E93" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G93" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J93" t="n">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -4529,26 +4529,26 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Vikram_93</t>
+          <t>STU093</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>6.31</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="C94" t="n">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="D94" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E94" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="F94" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -4556,43 +4556,43 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="J94" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Arjun_94</t>
+          <t>STU094</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>8.039999999999999</v>
+        <v>7.65</v>
       </c>
       <c r="C95" t="n">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="D95" t="n">
+        <v>51</v>
+      </c>
+      <c r="E95" t="n">
         <v>43</v>
-      </c>
-      <c r="E95" t="n">
-        <v>54</v>
       </c>
       <c r="F95" t="n">
         <v>2</v>
       </c>
       <c r="G95" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="J95" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -4617,37 +4617,37 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Harsha_95</t>
+          <t>STU095</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>8.859999999999999</v>
+        <v>7.71</v>
       </c>
       <c r="C96" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D96" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E96" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="F96" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="J96" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -4655,76 +4655,76 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>8.19</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Neha_96</t>
+          <t>STU096</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>9.859999999999999</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="C97" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D97" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E97" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J97" t="n">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>8.31</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Nikhil_97</t>
+          <t>STU097</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>8.41</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="C98" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D98" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E98" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="F98" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -4732,54 +4732,54 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J98" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Varun_98</t>
+          <t>STU098</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>8.529999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="C99" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D99" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E99" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F99" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G99" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="J99" t="n">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -4793,23 +4793,23 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Varun_99</t>
+          <t>STU099</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>5.81</v>
+        <v>7.53</v>
       </c>
       <c r="C100" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="D100" t="n">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="E100" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F100" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
         <v>3</v>
@@ -4820,54 +4820,54 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J100" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Not Placed</t>
+          <t>Placed</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>13.32</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sai_100</t>
+          <t>STU100</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>8.35</v>
+        <v>5.82</v>
       </c>
       <c r="C101" t="n">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="D101" t="n">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="E101" t="n">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c r="F101" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="J101" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
